--- a/LISTAS_ORDENADAS/MA/Soportes y escuadras/ESCUADRA ANGULO DISMAY.xlsx
+++ b/LISTAS_ORDENADAS/MA/Soportes y escuadras/ESCUADRA ANGULO DISMAY.xlsx
@@ -690,14 +690,9 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="20" t="n">
-        <v>45202.60863689835</v>
-      </c>
-    </row>
-    <row r="2"/>
-    <row r="3"/>
-    <row r="4"/>
-    <row r="5"/>
-    <row r="6"/>
+        <v>45266</v>
+      </c>
+    </row>
     <row r="7" ht="22.5" customHeight="1" s="16">
       <c r="A7" s="15" t="inlineStr">
         <is>
@@ -906,26 +901,6 @@
         <v>185</v>
       </c>
     </row>
-    <row r="22"/>
-    <row r="23"/>
-    <row r="24"/>
-    <row r="25"/>
-    <row r="26"/>
-    <row r="27"/>
-    <row r="28"/>
-    <row r="29"/>
-    <row r="30"/>
-    <row r="31"/>
-    <row r="32"/>
-    <row r="33"/>
-    <row r="34"/>
-    <row r="35"/>
-    <row r="36"/>
-    <row r="37"/>
-    <row r="38"/>
-    <row r="39"/>
-    <row r="40"/>
-    <row r="41"/>
     <row r="42">
       <c r="B42" s="6" t="inlineStr">
         <is>
@@ -935,10 +910,10 @@
     </row>
   </sheetData>
   <mergeCells count="4">
+    <mergeCell ref="A11:E11"/>
     <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A12:E12"/>
     <mergeCell ref="A10:E10"/>
-    <mergeCell ref="A11:E11"/>
-    <mergeCell ref="A12:E12"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup orientation="portrait" paperSize="9" horizontalDpi="0" verticalDpi="0"/>
